--- a/cloudflare-deploy/public/library/branch/hq-en.xlsx
+++ b/cloudflare-deploy/public/library/branch/hq-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1673,6 +1673,60 @@
       <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Classes (teachers) where praise points flow well tend to have higher re-enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>📢</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Notice Studio (Poster + Popup)</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Go to the admin menu Notification Center → 📢 Notice Studio. → In the ①Create tab, design a poster with text, images, and video (resize · save on server · reuse). → Press ‘📢 Publish as popup’ on the finished poster to auto-switch to the ②Publish·Popup tab. → In the publish tab, set the display period / stop and publish it as a student-app popup.</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>Promoting an event takes just one flow: ‘Create → Publish as popup’ right away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Command the AI Operations Assistant</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Type a command in the top search bar or speak with the 🎤 mic. → e.g. “Take me to teacher Kim Minji's schedule” → auto-finds that teacher in the weekly schedule and opens it. → e.g. “Open auto-scheduling,” “Go to settlement” to navigate menus. → Press ‘Go now →’ on the AI response card to move to that screen.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>When you can't recall a menu name, just say what you want to do — it finds its way there.</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3516,8 +3570,304 @@
       <c r="E165" s="33" t="n"/>
       <c r="F165" s="33" t="n"/>
     </row>
+    <row r="167" ht="26" customHeight="1">
+      <c r="A167" s="21" t="inlineStr">
+        <is>
+          <t>16  📢 Notice Studio (Poster + Popup)  —  Design notice/event posters and push them as app popups</t>
+        </is>
+      </c>
+      <c r="B167" s="22" t="n"/>
+      <c r="C167" s="22" t="n"/>
+      <c r="D167" s="22" t="n"/>
+      <c r="E167" s="22" t="n"/>
+      <c r="F167" s="22" t="n"/>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="23" t="inlineStr">
+        <is>
+          <t>📖 This merges the old ‘Poster Maker’ and ‘Popup Notice’ tools into one place. In the ①Create tab you design a notice/event poster, then hand it straight to the ②Publish·Popup tab to show it as a popup in your branch's student app.</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="n"/>
+      <c r="C168" s="24" t="n"/>
+      <c r="D168" s="24" t="n"/>
+      <c r="E168" s="24" t="n"/>
+      <c r="F168" s="24" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B169" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B170" s="28" t="inlineStr">
+        <is>
+          <t>Go to the admin menu Notification Center → 📢 Notice Studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B171" s="28" t="inlineStr">
+        <is>
+          <t>In the ①Create tab, design a poster with text, images, and video (resize · save on server · reuse).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B172" s="28" t="inlineStr">
+        <is>
+          <t>Press ‘📢 Publish as popup’ on the finished poster to auto-switch to the ②Publish·Popup tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B173" s="28" t="inlineStr">
+        <is>
+          <t>In the publish tab, set the display period / stop and publish it as a student-app popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="24" customHeight="1">
+      <c r="A174" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B174" s="30" t="inlineStr">
+        <is>
+          <t>Poster creation and popup publishing flow through one screen, two tabs — no more confusion.</t>
+        </is>
+      </c>
+      <c r="C174" s="31" t="n"/>
+      <c r="D174" s="31" t="n"/>
+      <c r="E174" s="31" t="n"/>
+      <c r="F174" s="31" t="n"/>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="A175" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B175" s="30" t="inlineStr">
+        <is>
+          <t>Posters you make can be saved and reused.</t>
+        </is>
+      </c>
+      <c r="C175" s="31" t="n"/>
+      <c r="D175" s="31" t="n"/>
+      <c r="E175" s="31" t="n"/>
+      <c r="F175" s="31" t="n"/>
+    </row>
+    <row r="176" ht="24" customHeight="1">
+      <c r="A176" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B176" s="30" t="inlineStr">
+        <is>
+          <t>Whichever route you enter from — AI assistant or sidebar search — the correct tab opens.</t>
+        </is>
+      </c>
+      <c r="C176" s="31" t="n"/>
+      <c r="D176" s="31" t="n"/>
+      <c r="E176" s="31" t="n"/>
+      <c r="F176" s="31" t="n"/>
+    </row>
+    <row r="177" ht="26" customHeight="1">
+      <c r="A177" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Existing posters/popups are preserved (it was only merged, nothing was deleted).</t>
+        </is>
+      </c>
+      <c r="B177" s="35" t="n"/>
+      <c r="C177" s="35" t="n"/>
+      <c r="D177" s="35" t="n"/>
+      <c r="E177" s="35" t="n"/>
+      <c r="F177" s="35" t="n"/>
+    </row>
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Promoting an event takes just one flow: ‘Create → Publish as popup’ right away.</t>
+        </is>
+      </c>
+      <c r="B178" s="33" t="n"/>
+      <c r="C178" s="33" t="n"/>
+      <c r="D178" s="33" t="n"/>
+      <c r="E178" s="33" t="n"/>
+      <c r="F178" s="33" t="n"/>
+    </row>
+    <row r="180" ht="26" customHeight="1">
+      <c r="A180" s="21" t="inlineStr">
+        <is>
+          <t>17  🤖 Command the AI Operations Assistant  —  Navigate with one phrase: “Take me to ○○”</t>
+        </is>
+      </c>
+      <c r="B180" s="22" t="n"/>
+      <c r="C180" s="22" t="n"/>
+      <c r="D180" s="22" t="n"/>
+      <c r="E180" s="22" t="n"/>
+      <c r="F180" s="22" t="n"/>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="23" t="inlineStr">
+        <is>
+          <t>📖 Type what you want to do into the top search bar (or the bottom-right AI assistant) in plain language, and the AI understands and jumps straight to that screen. It now reliably follows navigation commands like ‘Take me to teacher ○○'s schedule’ or ‘Open auto-scheduling’.</t>
+        </is>
+      </c>
+      <c r="B181" s="24" t="n"/>
+      <c r="C181" s="24" t="n"/>
+      <c r="D181" s="24" t="n"/>
+      <c r="E181" s="24" t="n"/>
+      <c r="F181" s="24" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B182" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B183" s="28" t="inlineStr">
+        <is>
+          <t>Type a command in the top search bar or speak with the 🎤 mic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B184" s="28" t="inlineStr">
+        <is>
+          <t>e.g. “Take me to teacher Kim Minji's schedule” → auto-finds that teacher in the weekly schedule and opens it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B185" s="28" t="inlineStr">
+        <is>
+          <t>e.g. “Open auto-scheduling,” “Go to settlement” to navigate menus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B186" s="28" t="inlineStr">
+        <is>
+          <t>Press ‘Go now →’ on the AI response card to move to that screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="24" customHeight="1">
+      <c r="A187" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B187" s="30" t="inlineStr">
+        <is>
+          <t>Navigation commands actually navigate — far fewer ‘explain only, do nothing’ replies.</t>
+        </is>
+      </c>
+      <c r="C187" s="31" t="n"/>
+      <c r="D187" s="31" t="n"/>
+      <c r="E187" s="31" t="n"/>
+      <c r="F187" s="31" t="n"/>
+    </row>
+    <row r="188" ht="24" customHeight="1">
+      <c r="A188" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B188" s="30" t="inlineStr">
+        <is>
+          <t>Searching a schedule by teacher name auto-fills the search box + filters + scrolls.</t>
+        </is>
+      </c>
+      <c r="C188" s="31" t="n"/>
+      <c r="D188" s="31" t="n"/>
+      <c r="E188" s="31" t="n"/>
+      <c r="F188" s="31" t="n"/>
+    </row>
+    <row r="189" ht="24" customHeight="1">
+      <c r="A189" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B189" s="30" t="inlineStr">
+        <is>
+          <t>For data/statistics questions it also helps with card-style answers.</t>
+        </is>
+      </c>
+      <c r="C189" s="31" t="n"/>
+      <c r="D189" s="31" t="n"/>
+      <c r="E189" s="31" t="n"/>
+      <c r="F189" s="31" t="n"/>
+    </row>
+    <row r="190" ht="26" customHeight="1">
+      <c r="A190" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Commands that actually change things — ‘register · send · modify’ — ask for one more confirmation (a safety guard).</t>
+        </is>
+      </c>
+      <c r="B190" s="35" t="n"/>
+      <c r="C190" s="35" t="n"/>
+      <c r="D190" s="35" t="n"/>
+      <c r="E190" s="35" t="n"/>
+      <c r="F190" s="35" t="n"/>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · When you can't recall a menu name, just say what you want to do — it finds its way there.</t>
+        </is>
+      </c>
+      <c r="B191" s="33" t="n"/>
+      <c r="C191" s="33" t="n"/>
+      <c r="D191" s="33" t="n"/>
+      <c r="E191" s="33" t="n"/>
+      <c r="F191" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="150">
+  <mergeCells count="174">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
@@ -3526,6 +3876,7 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="A133:F133"/>
     <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B58:F58"/>
@@ -3533,6 +3884,7 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A144:F144"/>
+    <mergeCell ref="B170:F170"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A134:F134"/>
     <mergeCell ref="B157:F157"/>
@@ -3542,7 +3894,10 @@
     <mergeCell ref="A121:F121"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B186:F186"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B118:F118"/>
@@ -3559,12 +3914,14 @@
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B185:F185"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B176:F176"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="A141:F141"/>
@@ -3572,28 +3929,39 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B175:F175"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B148:F148"/>
+    <mergeCell ref="A190:F190"/>
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B171:F171"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
+    <mergeCell ref="A167:F167"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A114:F114"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B187:F187"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A178:F178"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B189:F189"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="A153:F153"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B188:F188"/>
     <mergeCell ref="B126:F126"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B109:F109"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="B150:F150"/>
@@ -3606,11 +3974,13 @@
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B161:F161"/>
+    <mergeCell ref="A181:F181"/>
     <mergeCell ref="B136:F136"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A180:F180"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
@@ -3621,11 +3991,13 @@
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A168:F168"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B163:F163"/>
     <mergeCell ref="B110:F110"/>
@@ -3652,6 +4024,7 @@
     <mergeCell ref="B119:F119"/>
     <mergeCell ref="A156:F156"/>
     <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="B127:F127"/>
@@ -3662,6 +4035,7 @@
     <mergeCell ref="B95:F95"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B169:F169"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B41:F41"/>

--- a/cloudflare-deploy/public/library/branch/hq-en.xlsx
+++ b/cloudflare-deploy/public/library/branch/hq-en.xlsx
@@ -1130,7 +1130,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/branch/hq-en.xlsx
+++ b/cloudflare-deploy/public/library/branch/hq-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1727,6 +1727,33 @@
       <c r="E20" s="15" t="inlineStr">
         <is>
           <t>When you can't recall a menu name, just say what you want to do — it finds its way there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Share Library Links via KakaoTalk</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>In the admin Library, press 💬 Copy KakaoTalk link next to the file. → Paste it into the KakaoTalk chat room. → Recipients tap the link to watch or download in original quality.</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>In a parents' group chat, one video-guide link does all the explaining.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3866,11 +3893,134 @@
       <c r="E191" s="33" t="n"/>
       <c r="F191" s="33" t="n"/>
     </row>
+    <row r="193" ht="26" customHeight="1">
+      <c r="A193" s="21" t="inlineStr">
+        <is>
+          <t>18  💬 Share Library Links via KakaoTalk  —  Send videos &amp; docs in original quality</t>
+        </is>
+      </c>
+      <c r="B193" s="22" t="n"/>
+      <c r="C193" s="22" t="n"/>
+      <c r="D193" s="22" t="n"/>
+      <c r="E193" s="22" t="n"/>
+      <c r="F193" s="22" t="n"/>
+    </row>
+    <row r="194" ht="42" customHeight="1">
+      <c r="A194" s="23" t="inlineStr">
+        <is>
+          <t>📖 Every guide and video in the library now has a '💬 Copy KakaoTalk link' button. Attaching a file to KakaoTalk crushes the quality, but sending a link plays the original as-is. One tap copies the link — guiding parents and teachers gets much easier.</t>
+        </is>
+      </c>
+      <c r="B194" s="24" t="n"/>
+      <c r="C194" s="24" t="n"/>
+      <c r="D194" s="24" t="n"/>
+      <c r="E194" s="24" t="n"/>
+      <c r="F194" s="24" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B195" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B196" s="28" t="inlineStr">
+        <is>
+          <t>In the admin Library, press 💬 Copy KakaoTalk link next to the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B197" s="28" t="inlineStr">
+        <is>
+          <t>Paste it into the KakaoTalk chat room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B198" s="28" t="inlineStr">
+        <is>
+          <t>Recipients tap the link to watch or download in original quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="24" customHeight="1">
+      <c r="A199" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B199" s="30" t="inlineStr">
+        <is>
+          <t>For videos, link sharing = original quality; file attachments degrade it.</t>
+        </is>
+      </c>
+      <c r="C199" s="31" t="n"/>
+      <c r="D199" s="31" t="n"/>
+      <c r="E199" s="31" t="n"/>
+      <c r="F199" s="31" t="n"/>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B200" s="30" t="inlineStr">
+        <is>
+          <t>Works the same for PDFs, PPTs, and videos anywhere in the library.</t>
+        </is>
+      </c>
+      <c r="C200" s="31" t="n"/>
+      <c r="D200" s="31" t="n"/>
+      <c r="E200" s="31" t="n"/>
+      <c r="F200" s="31" t="n"/>
+    </row>
+    <row r="201" ht="26" customHeight="1">
+      <c r="A201" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Anyone with the link can open it. For internal-only material, check who you share with.</t>
+        </is>
+      </c>
+      <c r="B201" s="35" t="n"/>
+      <c r="C201" s="35" t="n"/>
+      <c r="D201" s="35" t="n"/>
+      <c r="E201" s="35" t="n"/>
+      <c r="F201" s="35" t="n"/>
+    </row>
+    <row r="202" ht="30" customHeight="1">
+      <c r="A202" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · In a parents' group chat, one video-guide link does all the explaining.</t>
+        </is>
+      </c>
+      <c r="B202" s="33" t="n"/>
+      <c r="C202" s="33" t="n"/>
+      <c r="D202" s="33" t="n"/>
+      <c r="E202" s="33" t="n"/>
+      <c r="F202" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="174">
+  <mergeCells count="184">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B200:F200"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B90:F90"/>
@@ -3881,6 +4031,7 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A144:F144"/>
@@ -3895,6 +4046,7 @@
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B172:F172"/>
+    <mergeCell ref="A202:F202"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
@@ -3915,6 +4067,7 @@
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B185:F185"/>
+    <mergeCell ref="B199:F199"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B96:F96"/>
@@ -3955,6 +4108,7 @@
     <mergeCell ref="B189:F189"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B198:F198"/>
     <mergeCell ref="A153:F153"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B188:F188"/>
@@ -4003,6 +4157,7 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="A193:F193"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="A12:F12"/>
@@ -4018,6 +4173,7 @@
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="B151:F151"/>
+    <mergeCell ref="A194:F194"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A91:F91"/>
@@ -4025,9 +4181,11 @@
     <mergeCell ref="A156:F156"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B196:F196"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="B127:F127"/>
+    <mergeCell ref="A201:F201"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="A123:F123"/>
@@ -4038,6 +4196,7 @@
     <mergeCell ref="B169:F169"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B197:F197"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>

--- a/cloudflare-deploy/public/library/branch/hq-en.xlsx
+++ b/cloudflare-deploy/public/library/branch/hq-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1754,6 +1754,87 @@
       <c r="E21" s="20" t="inlineStr">
         <is>
           <t>In a parents' group chat, one video-guide link does all the explaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>🧭</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>A refreshed admin screen</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Press ‹ Collapse at the top of the left menu — it shrinks to an icon rail and the content gets wider. → Press the › button in the same place to expand it again. → The collapsed state is remembered for your next visit. → Too many menus to find one? Type its name into menu search at the top.</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Wide-table screens like settlement and payroll are far easier to read with the menu collapsed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>🌐</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>The interface language sets itself</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>If the account has a nationality on file, the right language appears automatically at login. → To change it manually, press the 🌐 EN / KR button at the top. → A manual choice is stored per account — several people can share one PC without interference. → Teacher guide slides and manuals switch to the English editions with it.</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Enter nationality when registering a new teacher and their very first login is in English — fewer support requests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Enrolment &amp; payment → automatic lesson creation</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Send students and parents the enrolment link. → They choose teacher → lesson options (weekly count, term, length) → days &amp; time. → The slot check must pass before the pay button unlocks (payment is blocked on a clash). → On confirmed payment, all sessions are created at once — verify in the admin lesson list. → Head-office prices and discount rates are managed on the pricing screen.</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Consultation → level test → send the enrolment link is the smoothest conversion path.</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4015,26 +4096,474 @@
       <c r="E202" s="33" t="n"/>
       <c r="F202" s="33" t="n"/>
     </row>
+    <row r="204" ht="26" customHeight="1">
+      <c r="A204" s="21" t="inlineStr">
+        <is>
+          <t>19  🧭 A refreshed admin screen  —  Collapsible sidebar · lighter background · line icons</t>
+        </is>
+      </c>
+      <c r="B204" s="22" t="n"/>
+      <c r="C204" s="22" t="n"/>
+      <c r="D204" s="22" t="n"/>
+      <c r="E204" s="22" t="n"/>
+      <c r="F204" s="22" t="n"/>
+    </row>
+    <row r="205" ht="42" customHeight="1">
+      <c r="A205" s="23" t="inlineStr">
+        <is>
+          <t>📖 The admin screen is now easier on the eyes and wider. The left menu collapses to a narrow icon rail via the ‹ Collapse button, and the background is now a consistent light tone. Menu icons were redrawn as line icons so labels read clearly.</t>
+        </is>
+      </c>
+      <c r="B205" s="24" t="n"/>
+      <c r="C205" s="24" t="n"/>
+      <c r="D205" s="24" t="n"/>
+      <c r="E205" s="24" t="n"/>
+      <c r="F205" s="24" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B206" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B207" s="28" t="inlineStr">
+        <is>
+          <t>Press ‹ Collapse at the top of the left menu — it shrinks to an icon rail and the content gets wider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B208" s="28" t="inlineStr">
+        <is>
+          <t>Press the › button in the same place to expand it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B209" s="28" t="inlineStr">
+        <is>
+          <t>The collapsed state is remembered for your next visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B210" s="28" t="inlineStr">
+        <is>
+          <t>Too many menus to find one? Type its name into menu search at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="24" customHeight="1">
+      <c r="A211" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B211" s="30" t="inlineStr">
+        <is>
+          <t>Screens full of tables and lists gain a lot of horizontal space.</t>
+        </is>
+      </c>
+      <c r="C211" s="31" t="n"/>
+      <c r="D211" s="31" t="n"/>
+      <c r="E211" s="31" t="n"/>
+      <c r="F211" s="31" t="n"/>
+    </row>
+    <row r="212" ht="24" customHeight="1">
+      <c r="A212" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B212" s="30" t="inlineStr">
+        <is>
+          <t>15 sub-pages were moved onto the same light theme, so the colour jump between screens is gone.</t>
+        </is>
+      </c>
+      <c r="C212" s="31" t="n"/>
+      <c r="D212" s="31" t="n"/>
+      <c r="E212" s="31" t="n"/>
+      <c r="F212" s="31" t="n"/>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B213" s="30" t="inlineStr">
+        <is>
+          <t>The collapse animation was removed so low-spec PCs don't stutter.</t>
+        </is>
+      </c>
+      <c r="C213" s="31" t="n"/>
+      <c r="D213" s="31" t="n"/>
+      <c r="E213" s="31" t="n"/>
+      <c r="F213" s="31" t="n"/>
+    </row>
+    <row r="214" ht="30" customHeight="1">
+      <c r="A214" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Wide-table screens like settlement and payroll are far easier to read with the menu collapsed.</t>
+        </is>
+      </c>
+      <c r="B214" s="33" t="n"/>
+      <c r="C214" s="33" t="n"/>
+      <c r="D214" s="33" t="n"/>
+      <c r="E214" s="33" t="n"/>
+      <c r="F214" s="33" t="n"/>
+    </row>
+    <row r="216" ht="26" customHeight="1">
+      <c r="A216" s="21" t="inlineStr">
+        <is>
+          <t>20  🌐 The interface language sets itself  —  Overseas staff and teachers start in English</t>
+        </is>
+      </c>
+      <c r="B216" s="22" t="n"/>
+      <c r="C216" s="22" t="n"/>
+      <c r="D216" s="22" t="n"/>
+      <c r="E216" s="22" t="n"/>
+      <c r="F216" s="22" t="n"/>
+    </row>
+    <row r="217" ht="42" customHeight="1">
+      <c r="A217" s="23" t="inlineStr">
+        <is>
+          <t>📖 Filipino teachers and overseas staff now start in English from the first screen. The interface language is decided from the account's nationality, and teacher accounts are always English regardless of name or previous choice. You can still switch any time with the 🌐 EN / KR button at the top.</t>
+        </is>
+      </c>
+      <c r="B217" s="24" t="n"/>
+      <c r="C217" s="24" t="n"/>
+      <c r="D217" s="24" t="n"/>
+      <c r="E217" s="24" t="n"/>
+      <c r="F217" s="24" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B218" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="30" customHeight="1">
+      <c r="A219" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B219" s="28" t="inlineStr">
+        <is>
+          <t>If the account has a nationality on file, the right language appears automatically at login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B220" s="28" t="inlineStr">
+        <is>
+          <t>To change it manually, press the 🌐 EN / KR button at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B221" s="28" t="inlineStr">
+        <is>
+          <t>A manual choice is stored per account — several people can share one PC without interference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B222" s="28" t="inlineStr">
+        <is>
+          <t>Teacher guide slides and manuals switch to the English editions with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B223" s="30" t="inlineStr">
+        <is>
+          <t>Teacher accounts are always English — no more getting lost in a Korean screen.</t>
+        </is>
+      </c>
+      <c r="C223" s="31" t="n"/>
+      <c r="D223" s="31" t="n"/>
+      <c r="E223" s="31" t="n"/>
+      <c r="F223" s="31" t="n"/>
+    </row>
+    <row r="224" ht="24" customHeight="1">
+      <c r="A224" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B224" s="30" t="inlineStr">
+        <is>
+          <t>Accounts with an English name no longer flip to Korean because of a Korean job title.</t>
+        </is>
+      </c>
+      <c r="C224" s="31" t="n"/>
+      <c r="D224" s="31" t="n"/>
+      <c r="E224" s="31" t="n"/>
+      <c r="F224" s="31" t="n"/>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B225" s="30" t="inlineStr">
+        <is>
+          <t>Language choice is isolated per account, so an overseas account isn't overwritten by someone else's pick.</t>
+        </is>
+      </c>
+      <c r="C225" s="31" t="n"/>
+      <c r="D225" s="31" t="n"/>
+      <c r="E225" s="31" t="n"/>
+      <c r="F225" s="31" t="n"/>
+    </row>
+    <row r="226" ht="26" customHeight="1">
+      <c r="A226" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Accounts with no nationality fall back to the old name/ID heuristic. Please fill in nationality when registering teachers.</t>
+        </is>
+      </c>
+      <c r="B226" s="35" t="n"/>
+      <c r="C226" s="35" t="n"/>
+      <c r="D226" s="35" t="n"/>
+      <c r="E226" s="35" t="n"/>
+      <c r="F226" s="35" t="n"/>
+    </row>
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Enter nationality when registering a new teacher and their very first login is in English — fewer support requests.</t>
+        </is>
+      </c>
+      <c r="B227" s="33" t="n"/>
+      <c r="C227" s="33" t="n"/>
+      <c r="D227" s="33" t="n"/>
+      <c r="E227" s="33" t="n"/>
+      <c r="F227" s="33" t="n"/>
+    </row>
+    <row r="229" ht="26" customHeight="1">
+      <c r="A229" s="21" t="inlineStr">
+        <is>
+          <t>21  💳 Enrolment &amp; payment → automatic lesson creation  —  Once payment is confirmed, every session is scheduled</t>
+        </is>
+      </c>
+      <c r="B229" s="22" t="n"/>
+      <c r="C229" s="22" t="n"/>
+      <c r="D229" s="22" t="n"/>
+      <c r="E229" s="22" t="n"/>
+      <c r="F229" s="22" t="n"/>
+    </row>
+    <row r="230" ht="42" customHeight="1">
+      <c r="A230" s="23" t="inlineStr">
+        <is>
+          <t>📖 On the Enrolment screen a student picks teacher, days and time and pays — and all lesson sessions are created automatically the moment payment is confirmed. The old manual timetable entry after payment is gone. If the slot clashes with an existing lesson, the conflict is detected before payment.</t>
+        </is>
+      </c>
+      <c r="B230" s="24" t="n"/>
+      <c r="C230" s="24" t="n"/>
+      <c r="D230" s="24" t="n"/>
+      <c r="E230" s="24" t="n"/>
+      <c r="F230" s="24" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B231" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="30" customHeight="1">
+      <c r="A232" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B232" s="28" t="inlineStr">
+        <is>
+          <t>Send students and parents the enrolment link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="30" customHeight="1">
+      <c r="A233" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B233" s="28" t="inlineStr">
+        <is>
+          <t>They choose teacher → lesson options (weekly count, term, length) → days &amp; time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B234" s="28" t="inlineStr">
+        <is>
+          <t>The slot check must pass before the pay button unlocks (payment is blocked on a clash).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B235" s="28" t="inlineStr">
+        <is>
+          <t>On confirmed payment, all sessions are created at once — verify in the admin lesson list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="30" customHeight="1">
+      <c r="A236" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B236" s="28" t="inlineStr">
+        <is>
+          <t>Head-office prices and discount rates are managed on the pricing screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="24" customHeight="1">
+      <c r="A237" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B237" s="30" t="inlineStr">
+        <is>
+          <t>Idempotent — a duplicated payment callback will not create the sessions twice.</t>
+        </is>
+      </c>
+      <c r="C237" s="31" t="n"/>
+      <c r="D237" s="31" t="n"/>
+      <c r="E237" s="31" t="n"/>
+      <c r="F237" s="31" t="n"/>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B238" s="30" t="inlineStr">
+        <is>
+          <t>Clashes with holidays or existing lessons are pushed back so the session count is still met.</t>
+        </is>
+      </c>
+      <c r="C238" s="31" t="n"/>
+      <c r="D238" s="31" t="n"/>
+      <c r="E238" s="31" t="n"/>
+      <c r="F238" s="31" t="n"/>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B239" s="30" t="inlineStr">
+        <is>
+          <t>Term discounts (6 months −5%, 12 months −10%) are applied to the amount automatically.</t>
+        </is>
+      </c>
+      <c r="C239" s="31" t="n"/>
+      <c r="D239" s="31" t="n"/>
+      <c r="E239" s="31" t="n"/>
+      <c r="F239" s="31" t="n"/>
+    </row>
+    <row r="240" ht="26" customHeight="1">
+      <c r="A240" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Stage 1 (enrol → pay → auto-create sessions) is live today. Later stages will follow.</t>
+        </is>
+      </c>
+      <c r="B240" s="35" t="n"/>
+      <c r="C240" s="35" t="n"/>
+      <c r="D240" s="35" t="n"/>
+      <c r="E240" s="35" t="n"/>
+      <c r="F240" s="35" t="n"/>
+    </row>
+    <row r="241" ht="30" customHeight="1">
+      <c r="A241" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Consultation → level test → send the enrolment link is the smoothest conversion path.</t>
+        </is>
+      </c>
+      <c r="B241" s="33" t="n"/>
+      <c r="C241" s="33" t="n"/>
+      <c r="D241" s="33" t="n"/>
+      <c r="E241" s="33" t="n"/>
+      <c r="F241" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="184">
+  <mergeCells count="220">
     <mergeCell ref="B106:F106"/>
+    <mergeCell ref="A205:F205"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B200:F200"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B209:F209"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="A133:F133"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B236:F236"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B238:F238"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A144:F144"/>
+    <mergeCell ref="B231:F231"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A134:F134"/>
@@ -4043,6 +4572,7 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A121:F121"/>
+    <mergeCell ref="B234:F234"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B172:F172"/>
@@ -4057,30 +4587,41 @@
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="B158:F158"/>
+    <mergeCell ref="A226:F226"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="B20:F20"/>
+    <mergeCell ref="A241:F241"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B213:F213"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="B135:F135"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B224:F224"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B185:F185"/>
     <mergeCell ref="B199:F199"/>
+    <mergeCell ref="B208:F208"/>
+    <mergeCell ref="A214:F214"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B105:F105"/>
+    <mergeCell ref="A204:F204"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B176:F176"/>
+    <mergeCell ref="B219:F219"/>
+    <mergeCell ref="B210:F210"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="B107:F107"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A240:F240"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B57:F57"/>
@@ -4090,6 +4631,7 @@
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="B171:F171"/>
+    <mergeCell ref="A230:F230"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B146:F146"/>
@@ -4101,9 +4643,12 @@
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B187:F187"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B239:F239"/>
+    <mergeCell ref="A216:F216"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A178:F178"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B207:F207"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B189:F189"/>
     <mergeCell ref="B45:F45"/>
@@ -4112,11 +4657,15 @@
     <mergeCell ref="A153:F153"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B188:F188"/>
+    <mergeCell ref="A227:F227"/>
     <mergeCell ref="B126:F126"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B218:F218"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="B232:F232"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="B150:F150"/>
     <mergeCell ref="B31:F31"/>
@@ -4133,12 +4682,14 @@
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="B145:F145"/>
+    <mergeCell ref="B225:F225"/>
     <mergeCell ref="A165:F165"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="B147:F147"/>
+    <mergeCell ref="A229:F229"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="B128:F128"/>
     <mergeCell ref="A83:F83"/>
@@ -4151,10 +4702,15 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B222:F222"/>
     <mergeCell ref="A168:F168"/>
+    <mergeCell ref="B212:F212"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B206:F206"/>
     <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B221:F221"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B237:F237"/>
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="A193:F193"/>
@@ -4165,6 +4721,7 @@
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B140:F140"/>
     <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B220:F220"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
@@ -4174,6 +4731,7 @@
     <mergeCell ref="B117:F117"/>
     <mergeCell ref="B151:F151"/>
     <mergeCell ref="A194:F194"/>
+    <mergeCell ref="B235:F235"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A91:F91"/>
@@ -4186,6 +4744,7 @@
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="B127:F127"/>
     <mergeCell ref="A201:F201"/>
+    <mergeCell ref="B211:F211"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="A123:F123"/>
